--- a/frontend/src/assests/files/sample.xlsx
+++ b/frontend/src/assests/files/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\내문서\cau-fix-web\frontend\src\assests\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA55D88-5388-4203-B051-D94075FCEC47}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F91D51D-A556-4FAC-8CF3-ADD25E36A9D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="113">
   <si>
     <t>번호</t>
   </si>
@@ -298,60 +298,6 @@
     <t>접수</t>
   </si>
   <si>
-    <t>2026-03-01 09:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-01 12:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-01 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-01 21:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-02 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-08 00:47</t>
-  </si>
-  <si>
-    <t>2026-03-12 00:47</t>
-  </si>
-  <si>
-    <t>2026-03-11 00:47</t>
-  </si>
-  <si>
-    <t>2026-03-13 00:47</t>
-  </si>
-  <si>
-    <t>2026-03-10 00:47</t>
-  </si>
-  <si>
-    <t>2026-03-09 00:47</t>
-  </si>
-  <si>
-    <t>2026-03-10 00:49</t>
-  </si>
-  <si>
-    <t>2026-03-07 00:49</t>
-  </si>
-  <si>
-    <t>2026-03-12 00:49</t>
-  </si>
-  <si>
-    <t>2026-03-13 00:49</t>
-  </si>
-  <si>
-    <t>2026-03-06 00:49</t>
-  </si>
-  <si>
-    <t>2026-03-09 00:49</t>
-  </si>
-  <si>
     <t>응급실 자동문 개폐 지연</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -429,6 +375,10 @@
   </si>
   <si>
     <t>응급실 출입 자동문이 환자 침대 이동 시 반응이 늦어 충돌 위험이 있습니다. 센서 감도 및 모터 상태 점검이 필요합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기/통신</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -495,11 +445,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -840,6 +791,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="10" max="10" width="16.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -901,8 +855,8 @@
       <c r="I2" t="s">
         <v>88</v>
       </c>
-      <c r="J2" t="s">
-        <v>92</v>
+      <c r="J2" s="2">
+        <v>46082.375</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -933,8 +887,8 @@
       <c r="I3" t="s">
         <v>89</v>
       </c>
-      <c r="J3" t="s">
-        <v>93</v>
+      <c r="J3" s="2">
+        <v>46054.5</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -965,8 +919,8 @@
       <c r="I4" t="s">
         <v>90</v>
       </c>
-      <c r="J4" t="s">
-        <v>94</v>
+      <c r="J4" s="2">
+        <v>46054.625</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -997,8 +951,8 @@
       <c r="I5" t="s">
         <v>90</v>
       </c>
-      <c r="J5" t="s">
-        <v>95</v>
+      <c r="J5" s="2">
+        <v>46082.75</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1029,8 +983,8 @@
       <c r="I6" t="s">
         <v>89</v>
       </c>
-      <c r="J6" t="s">
-        <v>96</v>
+      <c r="J6" s="2">
+        <v>46082.875</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1061,8 +1015,8 @@
       <c r="I7" t="s">
         <v>89</v>
       </c>
-      <c r="J7" t="s">
-        <v>97</v>
+      <c r="J7" s="2">
+        <v>46024</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1076,10 +1030,10 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G8" t="s">
         <v>70</v>
@@ -1087,8 +1041,8 @@
       <c r="I8" t="s">
         <v>91</v>
       </c>
-      <c r="J8" t="s">
-        <v>98</v>
+      <c r="J8" s="2">
+        <v>46030.032638888886</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1099,13 +1053,13 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
         <v>71</v>
@@ -1113,8 +1067,8 @@
       <c r="I9" t="s">
         <v>91</v>
       </c>
-      <c r="J9" t="s">
-        <v>99</v>
+      <c r="J9" s="2">
+        <v>45728.032638888886</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1128,10 +1082,10 @@
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="G10" t="s">
         <v>71</v>
@@ -1139,8 +1093,8 @@
       <c r="I10" t="s">
         <v>91</v>
       </c>
-      <c r="J10" t="s">
-        <v>100</v>
+      <c r="J10" s="2">
+        <v>45727.032638888886</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1154,10 +1108,10 @@
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="G11" t="s">
         <v>72</v>
@@ -1165,8 +1119,8 @@
       <c r="I11" t="s">
         <v>91</v>
       </c>
-      <c r="J11" t="s">
-        <v>100</v>
+      <c r="J11" s="2">
+        <v>45699.032638888886</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1180,10 +1134,10 @@
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G12" t="s">
         <v>73</v>
@@ -1191,8 +1145,8 @@
       <c r="I12" t="s">
         <v>90</v>
       </c>
-      <c r="J12" t="s">
-        <v>99</v>
+      <c r="J12" s="2">
+        <v>45700.032638888886</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1206,10 +1160,10 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F13" t="s">
         <v>62</v>
@@ -1220,8 +1174,8 @@
       <c r="I13" t="s">
         <v>89</v>
       </c>
-      <c r="J13" t="s">
-        <v>101</v>
+      <c r="J13" s="2">
+        <v>45701.032638888886</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1235,10 +1189,10 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="G14" t="s">
         <v>72</v>
@@ -1246,8 +1200,8 @@
       <c r="I14" t="s">
         <v>90</v>
       </c>
-      <c r="J14" t="s">
-        <v>102</v>
+      <c r="J14" s="2">
+        <v>45361.032638888886</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1261,10 +1215,10 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
         <v>62</v>
@@ -1275,8 +1229,8 @@
       <c r="I15" t="s">
         <v>89</v>
       </c>
-      <c r="J15" t="s">
-        <v>103</v>
+      <c r="J15" s="2">
+        <v>45360.032638888886</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1290,10 +1244,10 @@
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -1304,8 +1258,8 @@
       <c r="I16" t="s">
         <v>89</v>
       </c>
-      <c r="J16" t="s">
-        <v>103</v>
+      <c r="J16" s="2">
+        <v>45331.032638888886</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1319,10 +1273,10 @@
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
         <v>62</v>
@@ -1333,8 +1287,8 @@
       <c r="I17" t="s">
         <v>89</v>
       </c>
-      <c r="J17" t="s">
-        <v>98</v>
+      <c r="J17" s="2">
+        <v>45330.032638888886</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1359,8 +1313,8 @@
       <c r="I18" t="s">
         <v>88</v>
       </c>
-      <c r="J18" t="s">
-        <v>104</v>
+      <c r="J18" s="2">
+        <v>45332.03402777778</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1388,8 +1342,8 @@
       <c r="I19" t="s">
         <v>89</v>
       </c>
-      <c r="J19" t="s">
-        <v>105</v>
+      <c r="J19" s="2">
+        <v>45329.03402777778</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1414,8 +1368,8 @@
       <c r="I20" t="s">
         <v>91</v>
       </c>
-      <c r="J20" t="s">
-        <v>106</v>
+      <c r="J20" s="2">
+        <v>45303.03402777778</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1440,8 +1394,8 @@
       <c r="I21" t="s">
         <v>88</v>
       </c>
-      <c r="J21" t="s">
-        <v>107</v>
+      <c r="J21" s="2">
+        <v>45304.03402777778</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -1466,8 +1420,8 @@
       <c r="I22" t="s">
         <v>88</v>
       </c>
-      <c r="J22" t="s">
-        <v>108</v>
+      <c r="J22" s="2">
+        <v>45297.03402777778</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -1492,8 +1446,8 @@
       <c r="I23" t="s">
         <v>91</v>
       </c>
-      <c r="J23" t="s">
-        <v>104</v>
+      <c r="J23" s="2">
+        <v>45301.03402777778</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -1518,8 +1472,8 @@
       <c r="I24" t="s">
         <v>91</v>
       </c>
-      <c r="J24" t="s">
-        <v>104</v>
+      <c r="J24" s="2">
+        <v>45301.03402777778</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -1544,8 +1498,8 @@
       <c r="I25" t="s">
         <v>91</v>
       </c>
-      <c r="J25" t="s">
-        <v>104</v>
+      <c r="J25" s="2">
+        <v>45301.03402777778</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -1570,8 +1524,8 @@
       <c r="I26" t="s">
         <v>88</v>
       </c>
-      <c r="J26" t="s">
-        <v>109</v>
+      <c r="J26" s="2">
+        <v>46090.03402777778</v>
       </c>
     </row>
   </sheetData>
